--- a/data/trans_dic/IP44C$otros_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido algún retraso en otros pagos</t>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,71</t>
+          <t>0,66; 5,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,25</t>
+          <t>0,66; 6,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,9</t>
+          <t>1,12; 4,41</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,15</t>
+          <t>2,18; 7,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,66</t>
+          <t>2,49; 6,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,05</t>
+          <t>2,74; 5,82</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 53,33</t>
+          <t>4,5; 54,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,97</t>
+          <t>1,12; 6,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 32,93</t>
+          <t>3,34; 35,23</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,6</t>
+          <t>4,56; 11,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,98</t>
+          <t>3,96; 11,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,39</t>
+          <t>5,0; 9,91</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 22,83</t>
+          <t>4,49; 23,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,54</t>
+          <t>3,05; 5,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,04</t>
+          <t>4,29; 15,63</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6011</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>767; 6440</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>901; 8668</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2836; 11149</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7691</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10472</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18163</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4079; 13292</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6266; 17323</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11988; 25514</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>36527</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4997</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41524</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>8449; 102336</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2014; 12408</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12257; 129397</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12242</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24545</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7349; 18708</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7023; 20088</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16905; 33508</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>59082</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31161</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>90243</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>29306; 151302</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22711; 42436</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>59848; 218197</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$otros_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,54</t>
+          <t>0,69; 5,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,36</t>
+          <t>0,68; 6,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,41</t>
+          <t>1,08; 4,68</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,11</t>
+          <t>2,17; 6,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,9</t>
+          <t>2,42; 6,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,82</t>
+          <t>2,72; 6,11</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 54,45</t>
+          <t>4,62; 50,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,92</t>
+          <t>1,13; 6,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 35,23</t>
+          <t>3,41; 39,99</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,62</t>
+          <t>4,38; 11,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,33</t>
+          <t>4,16; 10,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,91</t>
+          <t>5,04; 10,0</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 23,2</t>
+          <t>4,53; 28,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,7</t>
+          <t>3,03; 5,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 15,63</t>
+          <t>4,34; 14,28</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>767; 6440</t>
+          <t>801; 6500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>901; 8668</t>
+          <t>926; 8891</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2836; 11149</t>
+          <t>2734; 11833</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4079; 13292</t>
+          <t>4060; 12789</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6266; 17323</t>
+          <t>6069; 16257</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11988; 25514</t>
+          <t>11903; 26758</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8449; 102336</t>
+          <t>8680; 94595</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2014; 12408</t>
+          <t>2026; 11515</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12257; 129397</t>
+          <t>12518; 146851</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7349; 18708</t>
+          <t>7052; 18516</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7023; 20088</t>
+          <t>7369; 18951</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16905; 33508</t>
+          <t>17056; 33835</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29306; 151302</t>
+          <t>29523; 187081</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22711; 42436</t>
+          <t>22570; 41086</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59848; 218197</t>
+          <t>60653; 199332</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$otros_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,59</t>
+          <t>0,72; 6,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,52</t>
+          <t>0,76; 5,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,68</t>
+          <t>1,05; 4,59</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,84</t>
+          <t>2,53; 7,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,47</t>
+          <t>2,31; 7,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,11</t>
+          <t>3,0; 6,52</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 50,33</t>
+          <t>0,93; 6,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,42</t>
+          <t>3,28; 14,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 39,99</t>
+          <t>2,57; 7,91</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,5</t>
+          <t>4,01; 11,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 10,69</t>
+          <t>4,63; 12,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 10,0</t>
+          <t>5,27; 11,05</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 28,69</t>
+          <t>3,13; 5,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,52</t>
+          <t>3,9; 7,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,28</t>
+          <t>3,76; 6,09</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5427</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>801; 6500</t>
+          <t>873; 7498</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>926; 8891</t>
+          <t>916; 6847</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2734; 11833</t>
+          <t>2544; 11102</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18197</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4060; 12789</t>
+          <t>5898; 16554</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6069; 16257</t>
+          <t>4170; 13961</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11903; 26758</t>
+          <t>12428; 27016</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36527</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41524</t>
+          <t>14206</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8680; 94595</t>
+          <t>1507; 10344</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026; 11515</t>
+          <t>5080; 21667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12518; 146851</t>
+          <t>8126; 25053</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>25041</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7052; 18516</t>
+          <t>6650; 19622</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7369; 18951</t>
+          <t>7448; 19390</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17056; 33835</t>
+          <t>17244; 36140</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90243</t>
+          <t>62871</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29523; 187081</t>
+          <t>21413; 39734</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22570; 41086</t>
+          <t>24034; 44862</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60653; 199332</t>
+          <t>48854; 79164</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$otros_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,72; 6,16</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 5,69</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,05; 4,59</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,53; 7,09</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,31; 7,72</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3,0; 6,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,93; 6,39</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3,28; 14,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,57; 7,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4,01; 11,83</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4,63; 12,04</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5,27; 11,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,13; 5,82</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3,9; 7,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3,76; 6,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.02372656466208168</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.02108300812867288</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.02241292360280863</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2537</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5427</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.007170863495031309</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.007609671893370773</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.01050496278982086</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>873; 7498</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>916; 6847</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2544; 11102</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.06155294924752709</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.05691113926958721</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.04585278311033194</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.04410060185068128</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.0436747708127475</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.04391473373836186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10298</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7899</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18197</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.02525800218713497</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.02305277345776091</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.02999168728828018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5898; 16554</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4170; 13961</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12428; 27016</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.0708906051342154</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.0771886054604875</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.06519775437781218</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.0262331042969458</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.06437658948965154</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.04487627756922752</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4246</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9961</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14206</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.009313559244569024</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.03283501587178857</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.02566820246824943</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1507; 10344</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5080; 21667</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8126; 25053</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.06391734932946494</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1400356956566117</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.079140459178404</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.07451979790439131</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.07873524451709099</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.07659568844318153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>12365</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>12676</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25041</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.04007813520252399</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.04626118154636095</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.05274727904924872</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6650; 19622</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>7448; 19390</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>17244; 36140</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1182537906098002</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1204399108456517</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1105484584356187</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.04362333402280392</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.05361046096996077</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04836267915267855</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>29798</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>33073</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>62871</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.03134814290776823</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.03895843596629513</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.03758021569283367</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>21413; 39734</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>24034; 44862</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>48854; 79164</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.05816785064211902</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.07272110391606745</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.06089613529880177</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2890</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5427</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>873</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>916</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7498</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6847</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>11102</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10298</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>7899</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>18197</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>5898</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4170</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>12428</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>16554</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>13961</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>27016</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4246</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>9961</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>14206</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1507</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>5080</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>8126</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>10344</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>21667</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>25053</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>12365</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>12676</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>25041</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6650</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>7448</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>17244</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>19622</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>19390</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>36140</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>29798</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>33073</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>62871</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>21413</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>24034</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>48854</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>39734</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>44862</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>79164</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>